--- a/sources/ogre_step6b.xlsx
+++ b/sources/ogre_step6b.xlsx
@@ -4799,7 +4799,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">

--- a/sources/ogre_step6b.xlsx
+++ b/sources/ogre_step6b.xlsx
@@ -728,6 +728,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
@@ -775,6 +780,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
@@ -820,6 +830,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>f9b36b8d-0849-48e2-82e6-616a4a498ad1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
